--- a/params.xlsx
+++ b/params.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -502,7 +502,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2020-2070, 5</t>
+          <t>2020-2070, 1</t>
         </is>
       </c>
     </row>
@@ -1031,6 +1031,116 @@
       <c r="D29" t="inlineStr">
         <is>
           <t>["copper"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cases</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>WHICH CASES ARE ADDED. Any number; battery packs and drivetrains join by being listed here once they have a case folder of their own. SAFE TO CHANGE: yes. A folder that does not exist is named and refused.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>combine.cases</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>["data_folder/bev_electronics_wiring", "data_folder/bev_electronics_boards"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>resource</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>THE METAL, AS EACH CASE NAMES IT. The wiring case resolves materials and calls it `copper`; the boards case resolves elements and calls it `Cu`. They are the same metal, and this is the only place that says so -- every name listed is looked for in every case, and whichever one that case has is the one used. SAFE TO CHANGE: yes. A case with none of these names is reported as contributing nothing rather than silently counting zero.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>combine.resource</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>["copper", "Cu"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>What the metal is called in the title. The names above are how the data spells it; this is how a reader says it. SAFE TO CHANGE: yes.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>combine.label</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>copper</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>whole</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>What the combined streams are called together, for the title. SAFE TO CHANGE: yes.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>combine.whole</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>BEV electronics</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>out_dir</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>WHERE THE COMBINED FIGURE GOES. Not any one case's folder: it belongs to none of them. SAFE TO CHANGE: yes.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>combine.out_dir</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>figures/combined</t>
         </is>
       </c>
     </row>

--- a/params.xlsx
+++ b/params.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -502,7 +502,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2020-2070, 1</t>
+          <t>2020-2070, 5</t>
         </is>
       </c>
     </row>
@@ -1031,116 +1031,6 @@
       <c r="D29" t="inlineStr">
         <is>
           <t>["copper"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>cases</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>WHICH CASES ARE ADDED. Any number; battery packs and drivetrains join by being listed here once they have a case folder of their own. SAFE TO CHANGE: yes. A folder that does not exist is named and refused.</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>combine.cases</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>["data_folder/bev_electronics_wiring", "data_folder/bev_electronics_boards"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>resource</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>THE METAL, AS EACH CASE NAMES IT. The wiring case resolves materials and calls it `copper`; the boards case resolves elements and calls it `Cu`. They are the same metal, and this is the only place that says so -- every name listed is looked for in every case, and whichever one that case has is the one used. SAFE TO CHANGE: yes. A case with none of these names is reported as contributing nothing rather than silently counting zero.</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>combine.resource</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>["copper", "Cu"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>What the metal is called in the title. The names above are how the data spells it; this is how a reader says it. SAFE TO CHANGE: yes.</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>combine.label</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>copper</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>whole</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>What the combined streams are called together, for the title. SAFE TO CHANGE: yes.</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>combine.whole</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>BEV electronics</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>out_dir</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>WHERE THE COMBINED FIGURE GOES. Not any one case's folder: it belongs to none of them. SAFE TO CHANGE: yes.</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>combine.out_dir</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>figures/combined</t>
         </is>
       </c>
     </row>

--- a/params.xlsx
+++ b/params.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>****************************************************************** WHICH PIPELINE RUNS.  Set it here, then press Run on the stages in order: 00, 01, 02, 03 -- or 99 to run the checks and the pipeline.  'data_folder/bev_electronics_wiring'  04_02  the wiring and the motors, as MATERIALS: copper, alalloy, fealloy 'data_folder/bev_electronics_boards'  04_02  the boards and the sensors, as ELEMENTS: Au, Ag, Pd, Cu, Nd 'data_folder/carcomposition_mockup'   04_01  whole cars, five drivetrains, as MATERIALS  ONE AT A TIME. They are different studies -- different networks, different coefficients, different layers -- and a result is reported for one of them, never for both together.  Nothing else changes when you switch: each case carries its own data and its own coefficients in its own folder. ****************************************************************** A folder holding an `input_data/`, written from the project root. `02_run_model.py --list` prints the folders that qualify. SAFE TO CHANGE: yes -- this is the setting that changes on most runs.</t>
+          <t>****************************************************************** WHICH PIPELINE RUNS.  Set it here, then press Run on the stages in order: 00, 01, 02, 03 -- or 99 to run the checks and the pipeline.  'data_folder/bev_electronics_wiring'  04_02  the wiring and the motors, as MATERIALS: copper, alalloy, fealloy 'data_folder/bev_electronics_boards'  04_02  the boards and the sensors, as ELEMENTS: Au, Ag, Pd, Cu, Nd 'data_folder/carcomposition_mockup'   04_01  whole cars, five drivetrains, as MATERIALS 'data_folder/battery'                 04_04  the pack, as ELEMENTS within COMPONENTS 'data_folder/tractionmotor'           04_03  disassembly into the hydrometallurgical long loop 'data_folder/tractionmotor_shortloop' 04_03  disassembly into the short loop, HD/HPMS 'data_folder/tractionmotor_shredder'  04_03  no disassembly: the motor goes to the shredder 'data_folder/tractionmotor_split'     04_03  a share between the long and the short loop  SEVERAL AT ONCE, SEPARATED BY SEMICOLONS. Naming more than one runs every one of them, in the order written, exactly as a case set up with scenarios runs all of its scenarios:  data_folder = 'data_folder/tractionmotor; data_folder/...shredder'  STILL ONE STUDY PER CASE. They are different networks with different coefficients and different layers, so each one is solved, written and reported on its own. Several in one run saves the four edits and four presses it used to take -- it does not combine them into one answer.  THIS IS THE ONLY PLACE THAT SAYS WHICH. Every stage falls back to it, and the folder argument the numbered scripts take is an override for a one-off run, not a second place to keep the answer. Leaving it pointing at a case that is not the one being worked on is how a run of the boards gets mistaken for a run of the battery -- pressing Run passes no argument, so the setting is what decides.  Nothing else changes when you switch: each case carries its own data and its own coefficients in its own folder. ****************************************************************** One folder holding an `input_data/`, written from the project root, or several separated by semicolons. SAFE TO CHANGE: yes -- this is the setting that changes on most runs.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>data_folder/bev_electronics_boards</t>
+          <t>data_folder/tractionmotor; data_folder/tractionmotor_shortloop; data_folder/tractionmotor_shredder; data_folder/tractionmotor_split</t>
         </is>
       </c>
     </row>
@@ -474,7 +474,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WHICH SCENARIO TO RUN.  Blank when the data has no scenario dimension, which is the case for every data folder in this repository today.  ONE RUN IS ONE SCENARIO, across all its years. Scenarios are independent here -- this model is pure flow-through, with no stock carried between runs -- so nothing is gained by solving several at once, and under the Monte Carlo it costs: the memory budget is already the binding constraint (DESIGN_monte_carlo.md section 2). Separate runs also means five scenarios on five cores, and a failure that loses one rather than all.  Comparing scenarios is ANALYSIS, done afterwards on the output files. The model produces one scenario's numbers and stops there.  If the data holds scenarios and this is left blank, the run stops and lists what it found rather than guessing. SAFE TO CHANGE: yes -- it must name a scenario present in inputs.csv.</t>
+          <t>WHICH SCENARIO TO RUN.  Blank runs every scenario the case declares.  LEFT BLANK ON PURPOSE. A scenario is a property of the CASE, not of the settings: the reference cases carry no Scenario column at all, so naming one here makes `chosen_scenario` refuse them -- 26 tests, tried. Blank lets each case answer for itself, which is why `run.data_folder` alone does not decide a run.  BLANK MEANS ALL OF THEM, one pass each, in the order the case lists them: the battery as S1, S2 and S3, the traction motor cases as EH, SH, UH and mix. Naming one here narrows the run to that one. See `src/upstream.scenarios_to_run`.  2026-09-25, CORRECTED. This used to say the battery was run with `--scenario S1` on the command line, and that a blank setting stopped the run and listed what it found rather than guessing. Neither is true any more: the numbered stages take no arguments at all, and blank has meant "all of them" since `scenarios_to_run` arrived.  ONE PASS IS STILL ONE SCENARIO, across all its years. Scenarios are independent here -- this model is pure flow-through, with no stock carried between runs -- and solving several in one pass would cost: the memory budget is already the binding constraint (DESIGN_monte_carlo.md section 2). All of them from one press is a LOOP over passes, not one larger solve.  THE CASE LOOP PUTS THIS BACK between cases. The scenario loop writes the current scenario into this field, so a run naming several cases restores whatever is set here before each one. Without that, every case after the first inherited the last scenario that ran and silently did only that one.  Comparing scenarios is ANALYSIS, done afterwards on the output files. The model produces each scenario's numbers and stops there. SAFE TO CHANGE: yes -- it must name a scenario the case's own data has.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -492,7 +492,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WHICH YEARS TO RUN.  Blank means every year the data holds.  ''               every year in inputs.csv '2030'           that one year '2030-2050'      that range, both ends included, every year in it '2030-2050,10'   that range, every 10th year: 2030, 2040, 2050 ',10'            every 10th year of the whole data  Real inflow data is annual -- the upstream arrays run 1975 to 2070 -- so a step is usually what you want rather than the full trajectory. It keeps the shape of the curve while cutting its size. The step counts by year value, not by row, so a gap in the data does not shift everything after it.  Several years in one run is normal, unlike scenarios which are one per run. Years are independent here too, but a result usually wants the trajectory rather than a point.  It matters for the Monte Carlo: 200,000 draws x 96 years is the memory problem in DESIGN_monte_carlo.md section 2, and the year axis is the most direct lever on it. SAFE TO CHANGE: yes -- it must match at least one year present in the data.</t>
+          <t>WHICH YEARS TO RUN.  Blank means every year the data holds.  ''               every year in inputs.csv '2030'           that one year '2030-2050'      that range, both ends included, every year in it '2030-2050,10'   that range, every 10th year: 2030, 2040, 2050 ',10'            every 10th year of the whole data  Real inflow data is annual -- the upstream arrays run 1975 to 2070 -- so a step is usually what you want rather than the full trajectory. It keeps the shape of the curve while cutting its size. The step counts by year value, not by row, so a gap in the data does not shift everything after it.  Several years in one run is normal, unlike scenarios which are one per run. Years are independent here too, but a result usually wants the trajectory rather than a point.  It matters for the Monte Carlo: 200,000 draws x 96 years is the memory problem in DESIGN_monte_carlo.md section 2, and the year axis is the most direct lever on it. SAFE TO CHANGE: yes -- it must match at least one year present in the data.  2026-09-17: STEP 5, NOT 1, AND THE BATTERY IS WHY. Its upstream export (`battery_recovery_draws`) holds 11 years, 2020-2070 step 5, while the electronics export holds all 51. `05_combine_cases.py` refuses cases whose spans differ -- they are added year by year -- so every case that is combined has to run on the grid the battery has. Step 1 is still correct for a case run on its own; it cannot be combined with the battery until upstream exports the battery at every year.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2020-2070, 1</t>
+          <t>2020-2070, 5</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WHICH RESOURCES THE FIGURES COVER.  Empty means every one the case resolves. Name a few to focus: ('copper',) draws only copper on routes.png, fate.png and the per-resource densities.  It narrows what is DRAWN and never what is solved. Every resource stays in recovery_results.xlsx and monte_carlo_summary.csv whatever this says, so nothing is lost by focusing -- which is the point: the boards case resolves twenty-odd elements and a reader usually wants two. SAFE TO CHANGE: yes. A name that no case has is ignored rather than silently producing an empty figure.</t>
+          <t>WHICH RESOURCES THE FIGURES COVER.  Empty means every one the case resolves. Name a few to focus: ('copper',) draws only copper on routes.png, fate.png and the per-resource densities.  It narrows what is DRAWN and never what is solved. Every resource stays in recovery_results.xlsx and monte_carlo_summary.csv whatever this says, so nothing is lost by focusing -- which is the point: the boards case resolves twenty-odd elements and a reader usually wants two. SAFE TO CHANGE: yes. A name that no case has is ignored rather than silently producing an empty figure.  2026-09-17: nickel, cobalt and lithium joined copper when the battery case arrived. Both spellings of copper are listed because the cases do not agree on it -- wiring resolves MATERIALS and calls it `copper`, boards and the battery resolve ELEMENTS and call it `Cu`. The other three are elements everywhere, so one spelling each.  2026-09-25: the rare earths and the other motor materials joined it. Until the mixed-depth fix this list matched nothing in the traction motor case -- it resolves copper at the MATERIAL layer and the figures only looked at the element layer -- so `chosen` fell back to "everything it can see", which was the four rare earths and nothing else. With the fix 'copper' matches, and a list of five would have narrowed the figures to copper alone and dropped the rare earths. Both belong in this study, so both are named.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>["copper"]</t>
+          <t>["copper", "Cu", "Ni", "Co", "Li", "Nd", "Pr", "Dy", "Tb", "aluminium", "steel", "lamination"]</t>
         </is>
       </c>
     </row>
@@ -1052,93 +1052,71 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>["data_folder/bev_electronics_wiring", "data_folder/bev_electronics_boards"]</t>
+          <t>["data_folder/bev_electronics_wiring", "data_folder/bev_electronics_boards", "data_folder/battery"]</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>resource</t>
+          <t>resources</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>THE METAL, AS EACH CASE NAMES IT. The wiring case resolves materials and calls it `copper`; the boards case resolves elements and calls it `Cu`. They are the same metal, and this is the only place that says so -- every name listed is looked for in every case, and whichever one that case has is the one used. SAFE TO CHANGE: yes. A case with none of these names is reported as contributing nothing rather than silently counting zero.</t>
+          <t>****************************************************************** WHICH METALS ARE DRAWN.  Every one of them, every time 04 is run: four metals x three scenarios is twelve sets of figures from one press of Run. Add a metal by adding a line.  'how a reader says it': ('every spelling the data uses',)  THE SPELLINGS ARE A LIST BECAUSE THE CASES DISAGREE. Wiring resolves MATERIALS and calls it `copper`; boards and the battery resolve ELEMENTS and call it `Cu`. They are the same metal and this is the only place that says so -- every spelling is looked for in every case, and whichever one that case has is the one used. Nickel, cobalt and lithium are elements everywhere, so one spelling each.  The label is what the figures are titled and named with, so `nickel` gives nickel_combined.png and the rest of its set.  SAFE TO CHANGE: yes. A case with none of a metal's spellings is reported as contributing nothing rather than silently counting zero. ******************************************************************  THE RARE EARTHS ARE NOT HERE, AND THAT IS DELIBERATE from 2026-09-25. This figure ADDS cases -- wiring, boards and the battery are different parts of one car -- and it runs over the BATTERY's scenarios, S1/S2/S3. Neither fits the rare earths: they are not affected by a battery chemistry scenario, and the traction motor cases that carry Pr and Tb are four COMPETING ROUTES for the same motors, so adding them would count one fleet four times. The wiring case already holds a `Motors` group as well, which disagrees with the traction motor export by a factor of three on total motor mass.  They are reported separately instead, by `tools/compare_routes.py`.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>combine.resource</t>
+          <t>combine.resources</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>["copper", "Cu"]</t>
+          <t>{'copper': ('copper', 'Cu'), 'nickel': ('Ni',), 'cobalt': ('Co',), 'lithium': ('Li',)}</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>label</t>
+          <t>whole</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>What the metal is called in the title. The names above are how the data spells it; this is how a reader says it. SAFE TO CHANGE: yes.</t>
+          <t>What the combined streams are called together, for the title. Updated 2026-09-17 when the battery joined `cases`: the figures were still titled 'BEV electronics' while drawing the battery's components alongside them. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>combine.label</t>
+          <t>combine.whole</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>copper</t>
+          <t>BEV electronics and battery</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>whole</t>
+          <t>out_dir</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>What the combined streams are called together, for the title. SAFE TO CHANGE: yes.</t>
+          <t>WHERE THE COMBINED FIGURE GOES. Not any one case's folder: it belongs to none of them. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>combine.whole</t>
+          <t>combine.out_dir</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
-        <is>
-          <t>BEV electronics</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>out_dir</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>WHERE THE COMBINED FIGURE GOES. Not any one case's folder: it belongs to none of them. SAFE TO CHANGE: yes.</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>combine.out_dir</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
         <is>
           <t>figures/combined</t>
         </is>

--- a/params.xlsx
+++ b/params.xlsx
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>****************************************************************** WHICH PIPELINE RUNS.  Set it here, then press Run on the stages in order: 00, 01, 02, 03 -- or 99 to run the checks and the pipeline.  'data_folder/bev_electronics_wiring'  04_02  the wiring and the motors, as MATERIALS: copper, alalloy, fealloy 'data_folder/bev_electronics_boards'  04_02  the boards and the sensors, as ELEMENTS: Au, Ag, Pd, Cu, Nd 'data_folder/carcomposition_mockup'   04_01  whole cars, five drivetrains, as MATERIALS 'data_folder/battery'                 04_04  the pack, as ELEMENTS within COMPONENTS 'data_folder/tractionmotor'           04_03  disassembly into the hydrometallurgical long loop 'data_folder/tractionmotor_shortloop' 04_03  disassembly into the short loop, HD/HPMS 'data_folder/tractionmotor_shredder'  04_03  no disassembly: the motor goes to the shredder 'data_folder/tractionmotor_split'     04_03  a share between the long and the short loop  SEVERAL AT ONCE, SEPARATED BY SEMICOLONS. Naming more than one runs every one of them, in the order written, exactly as a case set up with scenarios runs all of its scenarios:  data_folder = 'data_folder/tractionmotor; data_folder/...shredder'  STILL ONE STUDY PER CASE. They are different networks with different coefficients and different layers, so each one is solved, written and reported on its own. Several in one run saves the four edits and four presses it used to take -- it does not combine them into one answer.  THIS IS THE ONLY PLACE THAT SAYS WHICH. Every stage falls back to it, and the folder argument the numbered scripts take is an override for a one-off run, not a second place to keep the answer. Leaving it pointing at a case that is not the one being worked on is how a run of the boards gets mistaken for a run of the battery -- pressing Run passes no argument, so the setting is what decides.  Nothing else changes when you switch: each case carries its own data and its own coefficients in its own folder. ****************************************************************** One folder holding an `input_data/`, written from the project root, or several separated by semicolons. SAFE TO CHANGE: yes -- this is the setting that changes on most runs.</t>
+          <t>****************************************************************** WHICH PIPELINE RUNS.  Set it here, then press Run on the stages in order: 00, 01, 02, 03 -- or 99 to run the checks and the pipeline.  'data_folder/bev_electronics_wiring'  04_02  the wiring and the motors, as MATERIALS: copper, alalloy, fealloy 'data_folder/bev_electronics_boards'  04_02  the boards and the sensors, as ELEMENTS: Au, Ag, Pd, Cu, Nd 'data_folder/carcomposition_mockup'   04_01  whole cars, five drivetrains, as MATERIALS 'data_folder/battery'                 04_04  the pack, as ELEMENTS within COMPONENTS 'data_folder/tractionmotor'           04_03  the fleet: motors removed and disassembled, the rest shredded in the hulk, split at the review's step 2  SEVERAL AT ONCE, SEPARATED BY SEMICOLONS. Naming more than one runs every one of them, in the order written, exactly as a case set up with scenarios runs all of its scenarios:  data_folder = 'data_folder/bev_electronics_wiring; ' 'data_folder/bev_electronics_boards'  STILL ONE STUDY PER CASE. They are different networks with different coefficients and different layers, so each one is solved, written and reported on its own. Several in one run saves the four edits and four presses it used to take -- it does not combine them into one answer.  THIS IS THE ONLY PLACE THAT SAYS WHICH. Every stage falls back to it, and the folder argument the numbered scripts take is an override for a one-off run, not a second place to keep the answer. Leaving it pointing at a case that is not the one being worked on is how a run of the boards gets mistaken for a run of the battery -- pressing Run passes no argument, so the setting is what decides.  Nothing else changes when you switch: each case carries its own data and its own coefficients in its own folder. ****************************************************************** One folder holding an `input_data/`, written from the project root, or several separated by semicolons. SAFE TO CHANGE: yes -- this is the setting that changes on most runs.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>data_folder/tractionmotor; data_folder/tractionmotor_shortloop; data_folder/tractionmotor_shredder; data_folder/tractionmotor_split</t>
+          <t>data_folder/tractionmotor</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>****************************************************************** WHICH METALS ARE DRAWN.  Every one of them, every time 04 is run: four metals x three scenarios is twelve sets of figures from one press of Run. Add a metal by adding a line.  'how a reader says it': ('every spelling the data uses',)  THE SPELLINGS ARE A LIST BECAUSE THE CASES DISAGREE. Wiring resolves MATERIALS and calls it `copper`; boards and the battery resolve ELEMENTS and call it `Cu`. They are the same metal and this is the only place that says so -- every spelling is looked for in every case, and whichever one that case has is the one used. Nickel, cobalt and lithium are elements everywhere, so one spelling each.  The label is what the figures are titled and named with, so `nickel` gives nickel_combined.png and the rest of its set.  SAFE TO CHANGE: yes. A case with none of a metal's spellings is reported as contributing nothing rather than silently counting zero. ******************************************************************  THE RARE EARTHS ARE NOT HERE, AND THAT IS DELIBERATE from 2026-09-25. This figure ADDS cases -- wiring, boards and the battery are different parts of one car -- and it runs over the BATTERY's scenarios, S1/S2/S3. Neither fits the rare earths: they are not affected by a battery chemistry scenario, and the traction motor cases that carry Pr and Tb are four COMPETING ROUTES for the same motors, so adding them would count one fleet four times. The wiring case already holds a `Motors` group as well, which disagrees with the traction motor export by a factor of three on total motor mass.  They are reported separately instead, by `tools/compare_routes.py`.</t>
+          <t>****************************************************************** WHICH METALS ARE DRAWN.  Every one of them, every time 04 is run: four metals x three scenarios is twelve sets of figures from one press of Run. Add a metal by adding a line.  'how a reader says it': ('every spelling the data uses',)  THE SPELLINGS ARE A LIST BECAUSE THE CASES DISAGREE. Wiring resolves MATERIALS and calls it `copper`; boards and the battery resolve ELEMENTS and call it `Cu`. They are the same metal and this is the only place that says so -- every spelling is looked for in every case, and whichever one that case has is the one used. Nickel, cobalt and lithium are elements everywhere, so one spelling each.  The label is what the figures are titled and named with, so `nickel` gives nickel_combined.png and the rest of its set.  SAFE TO CHANGE: yes. A case with none of a metal's spellings is reported as contributing nothing rather than silently counting zero. ******************************************************************  THE RARE EARTHS ARE NOT HERE, AND THAT IS DELIBERATE from 2026-09-25. This figure ADDS cases -- wiring, boards and the battery are different parts of one car -- and it runs over the BATTERY's scenarios, S1/S2/S3. Neither fits the rare earths: they are not affected by a battery chemistry scenario, and the traction motor cases that carry Pr and Tb are four COMPETING ROUTES for the same motors, so adding them would count one fleet four times. The wiring case already holds a `Motors` group as well, which disagrees with the traction motor export by a factor of three on total motor mass.  The traction motors are their own study -- press Run on `03_tractionmotors.py` -- and it answers for one fleet, not four.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">

--- a/params.xlsx
+++ b/params.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WHICH RESOURCES THE FIGURES COVER.  Empty means every one the case resolves. Name a few to focus: ('copper',) draws only copper on routes.png, fate.png and the per-resource densities.  It narrows what is DRAWN and never what is solved. Every resource stays in recovery_results.xlsx and monte_carlo_summary.csv whatever this says, so nothing is lost by focusing -- which is the point: the boards case resolves twenty-odd elements and a reader usually wants two. SAFE TO CHANGE: yes. A name that no case has is ignored rather than silently producing an empty figure.  2026-09-17: nickel, cobalt and lithium joined copper when the battery case arrived. Both spellings of copper are listed because the cases do not agree on it -- wiring resolves MATERIALS and calls it `copper`, boards and the battery resolve ELEMENTS and call it `Cu`. The other three are elements everywhere, so one spelling each.  2026-09-25: the rare earths and the other motor materials joined it. Until the mixed-depth fix this list matched nothing in the traction motor case -- it resolves copper at the MATERIAL layer and the figures only looked at the element layer -- so `chosen` fell back to "everything it can see", which was the four rare earths and nothing else. With the fix 'copper' matches, and a list of five would have narrowed the figures to copper alone and dropped the rare earths. Both belong in this study, so both are named.</t>
+          <t>WHICH RESOURCES THE FIGURES COVER.  Empty means every one the case resolves. Name a few to focus: ('copper',) draws only copper on fate.png, account_&lt;r&gt;.png, fleet_&lt;r&gt;.png and the per-resource densities.  It narrows what is DRAWN and never what is solved. Every resource stays in recovery_results.xlsx and monte_carlo_summary.csv whatever this says, so nothing is lost by focusing -- which is the point: the boards case resolves twenty-odd elements and a reader usually wants two. SAFE TO CHANGE: yes. A name that no case has is ignored rather than silently producing an empty figure.  2026-09-17: nickel, cobalt and lithium joined copper when the battery case arrived. Both spellings of copper are listed because the cases do not agree on it -- wiring resolves MATERIALS and calls it `copper`, boards and the battery resolve ELEMENTS and call it `Cu`. The other three are elements everywhere, so one spelling each.  2026-09-25: the rare earths and the other motor materials joined it. Until the mixed-depth fix this list matched nothing in the traction motor case -- it resolves copper at the MATERIAL layer and the figures only looked at the element layer -- so `chosen` fell back to "everything it can see", which was the four rare earths and nothing else. With the fix 'copper' matches, and a list of five would have narrowed the figures to copper alone and dropped the rare earths. Both belong in this study, so both are named.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">

--- a/params.xlsx
+++ b/params.xlsx
@@ -1052,7 +1052,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>["data_folder/bev_electronics_wiring", "data_folder/bev_electronics_boards", "data_folder/battery"]</t>
+          <t>["data_folder/bev_electronics_wiring", "data_folder/bev_electronics_boards", "data_folder/battery", "data_folder/tractionmotor"]</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>****************************************************************** WHICH METALS ARE DRAWN.  Every one of them, every time 04 is run: four metals x three scenarios is twelve sets of figures from one press of Run. Add a metal by adding a line.  'how a reader says it': ('every spelling the data uses',)  THE SPELLINGS ARE A LIST BECAUSE THE CASES DISAGREE. Wiring resolves MATERIALS and calls it `copper`; boards and the battery resolve ELEMENTS and call it `Cu`. They are the same metal and this is the only place that says so -- every spelling is looked for in every case, and whichever one that case has is the one used. Nickel, cobalt and lithium are elements everywhere, so one spelling each.  The label is what the figures are titled and named with, so `nickel` gives nickel_combined.png and the rest of its set.  SAFE TO CHANGE: yes. A case with none of a metal's spellings is reported as contributing nothing rather than silently counting zero. ******************************************************************  THE RARE EARTHS ARE NOT HERE, AND THAT IS DELIBERATE from 2026-09-25. This figure ADDS cases -- wiring, boards and the battery are different parts of one car -- and it runs over the BATTERY's scenarios, S1/S2/S3. Neither fits the rare earths: they are not affected by a battery chemistry scenario, and the traction motor cases that carry Pr and Tb are four COMPETING ROUTES for the same motors, so adding them would count one fleet four times. The wiring case already holds a `Motors` group as well, which disagrees with the traction motor export by a factor of three on total motor mass.  The traction motors are their own study -- press Run on `03_tractionmotors.py` -- and it answers for one fleet, not four.</t>
+          <t>****************************************************************** WHICH METALS ARE DRAWN.  Every one of them, every time 04 is run: four metals x three scenarios is twelve sets of figures from one press of Run. Add a metal by adding a line.  'how a reader says it': ('every spelling the data uses',)  THE SPELLINGS ARE A LIST BECAUSE THE CASES DISAGREE. Wiring resolves MATERIALS and calls it `copper`; boards and the battery resolve ELEMENTS and call it `Cu`. They are the same metal and this is the only place that says so -- every spelling is looked for in every case, and whichever one that case has is the one used. Nickel, cobalt and lithium are elements everywhere, so one spelling each.  The label is what the figures are titled and named with, so `nickel` gives nickel_combined.png and the rest of its set.  SAFE TO CHANGE: yes. A case with none of a metal's spellings is reported as contributing nothing rather than silently counting zero. ******************************************************************  THE RARE EARTHS JOINED ON 2026-09-29, when the traction motor case did. They were left out while there were FOUR traction cases, because those were competing routes for the same motors and adding them would have counted one fleet four times. There is one traction case now -- both roads inside it, split at the review's step 2 -- so it adds like any other part of the car.  Nd and Dy are in the BOARDS case too, as sensor and actuator magnets. That is not a double count: a sensor magnet and a traction magnet are different components of the same vehicle, which is the same reason wiring copper and board copper are added.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>{'copper': ('copper', 'Cu'), 'nickel': ('Ni',), 'cobalt': ('Co',), 'lithium': ('Li',)}</t>
+          <t>{'copper': ('copper', 'Cu'), 'nickel': ('Ni',), 'cobalt': ('Co',), 'lithium': ('Li',), 'neodymium': ('Nd',), 'praseodymium': ('Pr',), 'dysprosium': ('Dy',), 'terbium': ('Tb',)}</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>BEV electronics and battery</t>
+          <t>BEV electronics, battery and traction motor</t>
         </is>
       </c>
     </row>

--- a/params.xlsx
+++ b/params.xlsx
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>****************************************************************** WHICH PIPELINE RUNS.  Set it here, then press Run on the stages in order: 00, 01, 02, 03 -- or 99 to run the checks and the pipeline.  'data_folder/bev_electronics_wiring'  04_02  the wiring and the motors, as MATERIALS: copper, alalloy, fealloy 'data_folder/bev_electronics_boards'  04_02  the boards and the sensors, as ELEMENTS: Au, Ag, Pd, Cu, Nd 'data_folder/carcomposition_mockup'   04_01  whole cars, five drivetrains, as MATERIALS 'data_folder/battery'                 04_04  the pack, as ELEMENTS within COMPONENTS 'data_folder/tractionmotor'           04_03  the fleet: motors removed and disassembled, the rest shredded in the hulk, split at the review's step 2  SEVERAL AT ONCE, SEPARATED BY SEMICOLONS. Naming more than one runs every one of them, in the order written, exactly as a case set up with scenarios runs all of its scenarios:  data_folder = 'data_folder/bev_electronics_wiring; ' 'data_folder/bev_electronics_boards'  STILL ONE STUDY PER CASE. They are different networks with different coefficients and different layers, so each one is solved, written and reported on its own. Several in one run saves the four edits and four presses it used to take -- it does not combine them into one answer.  THIS IS THE ONLY PLACE THAT SAYS WHICH. Every stage falls back to it, and the folder argument the numbered scripts take is an override for a one-off run, not a second place to keep the answer. Leaving it pointing at a case that is not the one being worked on is how a run of the boards gets mistaken for a run of the battery -- pressing Run passes no argument, so the setting is what decides.  Nothing else changes when you switch: each case carries its own data and its own coefficients in its own folder. ****************************************************************** One folder holding an `input_data/`, written from the project root, or several separated by semicolons. SAFE TO CHANGE: yes -- this is the setting that changes on most runs.</t>
+          <t>****************************************************************** WHICH PIPELINE RUNS.  Set it here, then press Run on the stages in order: 00, 01, 02, 03 -- or 99 to run the checks and the pipeline.  'data/bev_electronics_wiring'  04_02  the wiring and the motors, as MATERIALS: copper, alalloy, fealloy 'data/bev_electronics_boards'  04_02  the boards and the sensors, as ELEMENTS: Au, Ag, Pd, Cu, Nd 'data/carcomposition_mockup'   04_01  whole cars, five drivetrains, as MATERIALS 'data/battery'                 04_04  the pack, as ELEMENTS within COMPONENTS 'data/tractionmotor'           04_03  the fleet: motors removed and disassembled, the rest shredded in the hulk, split at the review's step 2  SEVERAL AT ONCE, SEPARATED BY SEMICOLONS. Naming more than one runs every one of them, in the order written, exactly as a case set up with scenarios runs all of its scenarios:  data_folder = 'data/bev_electronics_wiring; ' 'data/bev_electronics_boards'  STILL ONE STUDY PER CASE. They are different networks with different coefficients and different layers, so each one is solved, written and reported on its own. Several in one run saves the four edits and four presses it used to take -- it does not combine them into one answer.  THIS IS THE ONLY PLACE THAT SAYS WHICH. Every stage falls back to it, and the folder argument the numbered scripts take is an override for a one-off run, not a second place to keep the answer. Leaving it pointing at a case that is not the one being worked on is how a run of the boards gets mistaken for a run of the battery -- pressing Run passes no argument, so the setting is what decides.  Nothing else changes when you switch: each case carries its own data and its own coefficients in its own folder. ****************************************************************** One folder holding an `input_data/`, written from the project root, or several separated by semicolons. SAFE TO CHANGE: yes -- this is the setting that changes on most runs.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>data_folder/tractionmotor</t>
+          <t>data/tractionmotor</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>["data_folder/bev_electronics_wiring", "data_folder/bev_electronics_boards", "data_folder/battery", "data_folder/tractionmotor"]</t>
+          <t>["data/bev_electronics_wiring", "data/bev_electronics_boards", "data/battery", "data/tractionmotor"]</t>
         </is>
       </c>
     </row>

--- a/params.xlsx
+++ b/params.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -531,295 +531,297 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>working_unit</t>
+          <t>variants</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>THE MASS UNIT THIS PROJECT WORKS IN. Every inflow is converted into this on load, from whatever its own file declares in the 'Unit' column, and every number the model writes is in it.  This used to be a check rather than a conversion: a file in another unit was reported and left alone, and converting it was a manual step. That is a poor arrangement when three units are genuinely in play -- the data folders here are written in Mg, the upstream pipeline delivers kt, and results are wanted in kg -- because the manual step can be forgotten and forgetting it is invisible. The model multiplies fractions, so a factor of 1000 leaves every ratio in the output looking perfectly reasonable.  Data files are NOT edited to match this. They keep saying what they are; this says what the answer should be in.  Worth knowing: no single unit suits both ends of this model. A year's collected fleet is around 500 kt and the gold in it is a few tonnes -- 500,000,000 kg against 3,000 kg. Figures therefore choose their own display unit per panel (src/units.py, scale_for); this setting governs the arithmetic and the output files. SAFE TO CHANGE: yes. Any unit in MASS_UNITS in src/units.py.</t>
+          <t>WHICH VERSION OF THE COEFFICIENTS TO USE, where a case offers more than one. Added 2026-10-08. A case can hold several versions of some of its coefficients in the SAME workbook -- rows tagged in the `variant` column of `TCs` and `TCs_improved` -- and this setting picks one of each:  tc_set          which set of coefficients drives the recovery own   your own numbers (the report's Table 2 for the hydrometallurgical road); where you have none -- pyrometallurgy, direct recycling, the split between roads, sodium -- the paper's REC numbers are borrowed and the tags say so BAU   the paper's business-as-usual numbers throughout REC   the paper's recovery scenario (EU targets met on time)  sodium_route    how sodium-ion cells are treated mechanical          mechanical treatment only, as in the paper mechanical_direct   part of the cells goes to direct recycling instead (prepared, placeholder numbers)  Several are separated by semicolons, exactly as `data_folder` is: variants = 'tc_set=REC; sodium_route=mechanical'  A case that offers none of these ignores this setting, so the electronics and traction motor cases are not affected. A case that offers a choice this setting does not make is REFUSED, naming what it offers: a silent default would give an answer that looks like any other.  Results of different choices are written to different folders -- the choice is part of the path, like the scenario -- so a REC run never overwrites an `own` run. SAFE TO CHANGE: yes -- it must name a choice the case offers.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>run.working_unit</t>
+          <t>run.variants</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>tc_set=own; sodium_route=mechanical</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>draw_structure</t>
+          <t>working_unit</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ALSO DRAW THE STRUCTURE DIAGRAM WHEN THE MODEL RUNS. The structure diagram shows how the flows connect and the transfer coefficients behind each arrow. It is not a picture of a result -- it only changes when the TC table changes -- so it is a switch rather than something that always happens. The Sankey figures are not a switch: they are drawn on every run, because they ARE the result and should never be out of step with it. SAFE TO CHANGE: yes. Set to False to skip the structure diagram; you can still draw it any time with:  ./.venv/bin/python tools/plot_structure.py</t>
+          <t>THE MASS UNIT THIS PROJECT WORKS IN. Every inflow is converted into this on load, from whatever its own file declares in the 'Unit' column, and every number the model writes is in it.  This used to be a check rather than a conversion: a file in another unit was reported and left alone, and converting it was a manual step. That is a poor arrangement when three units are genuinely in play -- the data folders here are written in Mg, the upstream pipeline delivers kt, and results are wanted in kg -- because the manual step can be forgotten and forgetting it is invisible. The model multiplies fractions, so a factor of 1000 leaves every ratio in the output looking perfectly reasonable.  Data files are NOT edited to match this. They keep saying what they are; this says what the answer should be in.  Worth knowing: no single unit suits both ends of this model. A year's collected fleet is around 500 kt and the gold in it is a few tonnes -- 500,000,000 kg against 3,000 kg. Figures therefore choose their own display unit per panel (src/units.py, scale_for); this setting governs the arithmetic and the output files. SAFE TO CHANGE: yes. Any unit in MASS_UNITS in src/units.py.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>run.draw_structure</t>
-        </is>
-      </c>
-      <c r="D7" t="b">
-        <v>1</v>
+          <t>run.working_unit</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>upstream_root</t>
+          <t>draw_structure</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WHERE THE UPSTREAM PROJECT IS, as a path from this project's root. The two repositories sit side by side, so the default works on any machine that has both checked out, without hard-coding a home directory. Written relative rather than absolute deliberately: the absolute path differs between the two Macs this project is worked on, and did so again when the folder moved into iCloud. SAFE TO CHANGE: yes -- it must point at the RAWCLICStockAndFlow checkout.</t>
+          <t>ALSO DRAW THE STRUCTURE DIAGRAM WHEN THE MODEL RUNS. The structure diagram shows how the flows connect and the transfer coefficients behind each arrow. It is not a picture of a result -- it only changes when the TC table changes -- so it is a switch rather than something that always happens. The Sankey figures are not a switch: they are drawn on every run, because they ARE the result and should never be out of step with it. SAFE TO CHANGE: yes. Set to False to skip the structure diagram; you can still draw it any time with:  ./.venv/bin/python tools/plot_structure.py</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>data.upstream_root</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>../RAWCLICStockAndFlow</t>
-        </is>
+          <t>run.draw_structure</t>
+        </is>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>inflow_draws_dir</t>
+          <t>upstream_root</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BY CASE (`upstream_dir` in source.csv). WHERE THE PER-CHILD INFLOW DRAWS ARE, under `upstream_root`. One `.npy` per child per flow, each of shape (draws, years), in kt. The scenario named in `run.scenario` is appended to this path.  These are written by a year-sliced export step in the upstream stage -- built for 04_02, to be mirrored for the others. Recomputing them here would mean duplicating that stage's segment splitting and draw pairing, and that pipeline's own header records three separate occasions where a stage reconstructed another stage's numbers and diverged silently. Read the real draws; do not re-derive them. SAFE TO CHANGE: yes -- but prefer saying it in the case's source.csv.</t>
+          <t>WHERE THE UPSTREAM PROJECT IS, as a path from this project's root. The two repositories sit side by side, so the default works on any machine that has both checked out, without hard-coding a home directory. Written relative rather than absolute deliberately: the absolute path differs between the two Macs this project is worked on, and did so again when the folder moved into iCloud. SAFE TO CHANGE: yes -- it must point at the RAWCLICStockAndFlow checkout.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>data.inflow_draws_dir</t>
+          <t>data.upstream_root</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>data/processed/element_draws</t>
+          <t>../RAWCLICStockAndFlow</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>draws</t>
+          <t>inflow_draws_dir</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HOW MANY OF THE DRAWS TO USE.  The upstream arrays hold 200,000. Lower this while developing: the memory arithmetic in DESIGN_monte_carlo.md section 2 is unforgiving at full width, and a few thousand draws is enough to see whether the machinery is correct. Raise it for a result that will be reported. Draws are taken from the front of the array, never sampled at random, so that a run at 5,000 is a strict prefix of a run at 200,000 and the two can be compared directly. SAFE TO CHANGE: yes. A whole number above zero, at most what the arrays hold.</t>
+          <t>BY CASE (`upstream_dir` in source.csv). WHERE THE PER-CHILD INFLOW DRAWS ARE, under `upstream_root`. One `.npy` per child per flow, each of shape (draws, years), in kt. The scenario named in `run.scenario` is appended to this path.  These are written by a year-sliced export step in the upstream stage -- built for 04_02, to be mirrored for the others. Recomputing them here would mean duplicating that stage's segment splitting and draw pairing, and that pipeline's own header records three separate occasions where a stage reconstructed another stage's numbers and diverged silently. Read the real draws; do not re-derive them. SAFE TO CHANGE: yes -- but prefer saying it in the case's source.csv.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>data.draws</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>200000</v>
+          <t>data.inflow_draws_dir</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>data/processed/element_draws</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>upstream_flow</t>
+          <t>draws</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BY CASE (`flow` in source.csv). WHICH UPSTREAM FLOW IS THE INFLOW TO RECOVERY. Upstream reports three: what entered the fleet, what left it, and what was collected for recycling. Recovery starts from what was collected -- the other two are the fleet's own story and are not handed to a recycler. SAFE TO CHANGE: yes. One of 'collected', 'outflow', 'inflow'.</t>
+          <t>HOW MANY OF THE DRAWS TO USE.  The upstream arrays hold 200,000. Lower this while developing: the memory arithmetic in DESIGN_monte_carlo.md section 2 is unforgiving at full width, and a few thousand draws is enough to see whether the machinery is correct. Raise it for a result that will be reported. Draws are taken from the front of the array, never sampled at random, so that a run at 5,000 is a strict prefix of a run at 200,000 and the two can be compared directly. SAFE TO CHANGE: yes. A whole number above zero, at most what the arrays hold.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>data.upstream_flow</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
+          <t>data.draws</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>200000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>upstream_flow</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BY CASE (`product` in source.csv). WHAT THE PRODUCT IS CALLED, at Layer 1. Whatever the upstream item is: 'BEV', 'PVPanel', 'Battery'. It is the parent every composition share is a share OF, and it appears in the output rows, so it should read as the thing being recycled. SAFE TO CHANGE: yes -- it is a label, and nothing matches on it.</t>
+          <t>BY CASE (`flow` in source.csv). WHICH UPSTREAM FLOW IS THE INFLOW TO RECOVERY. Upstream reports three: what entered the fleet, what left it, and what was collected for recycling. Recovery starts from what was collected -- the other two are the fleet's own story and are not handed to a recycler. SAFE TO CHANGE: yes. One of 'collected', 'outflow', 'inflow'.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>data.product</t>
+          <t>data.upstream_flow</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BEV</t>
+          <t>collected</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>inflow_flow_id</t>
+          <t>product</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BY CASE (`inflow_flow_id` in source.csv). WHAT THE INFLOW FLOW IS CALLED. The flow the upstream mass arrives in, and therefore the one the first process reads from. It must match the Input_FlowID of the first row in processes.csv. SAFE TO CHANGE: yes, together with processes.csv.</t>
+          <t>BY CASE (`product` in source.csv). WHAT THE PRODUCT IS CALLED, at Layer 1. Whatever the upstream item is: 'BEV', 'PVPanel', 'Battery'. It is the parent every composition share is a share OF, and it appears in the output rows, so it should read as the thing being recycled. SAFE TO CHANGE: yes -- it is a label, and nothing matches on it.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>data.inflow_flow_id</t>
+          <t>data.product</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>F_collected</t>
+          <t>BEV</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>material_suffix</t>
+          <t>inflow_flow_id</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BY CASE (`material_suffix` in source.csv). Used only where the upstream child is an ELEMENT; a case whose children are already materials leaves it blank and gets no placeholder. See `child_layer` in src/source.py. WHAT THE PLACEHOLDER MATERIAL LAYER IS CALLED, appended to the group name. It holds what the upstream file names do NOT resolve into a material. A file named &lt;element&gt;__&lt;material&gt;__&lt;group&gt; puts its material at Layer 3 in its own right; where there is no such file the element's material is unknown, and the placeholder is where it sits. An export with none of them gives one placeholder per group holding the whole of it, which is what every case read before 2026-08-31. See CASES.md, `child_layer`. SAFE TO CHANGE: yes -- it is a label.</t>
+          <t>BY CASE (`inflow_flow_id` in source.csv). WHAT THE INFLOW FLOW IS CALLED. The flow the upstream mass arrives in, and therefore the one the first process reads from. It must match the Input_FlowID of the first row in processes.csv. SAFE TO CHANGE: yes, together with processes.csv.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>data.material_suffix</t>
+          <t>data.inflow_flow_id</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>_mixed</t>
+          <t>F_collected</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>group_marker</t>
+          <t>material_suffix</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BY CASE (`group_marker` in source.csv). HOW THE UPSTREAM FILES NAME A GROUP'S OWN MASS. Files are `&lt;child&gt;__&lt;parent&gt;.npy`, and the group's own mass is written as `&lt;group_marker&gt;__&lt;group&gt;.npy`. Only change it if the upstream export changes its naming. SAFE TO CHANGE: yes, together with the upstream export.</t>
+          <t>BY CASE (`material_suffix` in source.csv). Used only where the upstream child is an ELEMENT; a case whose children are already materials leaves it blank and gets no placeholder. See `child_layer` in src/source.py. WHAT THE PLACEHOLDER MATERIAL LAYER IS CALLED, appended to the group name. It holds what the upstream file names do NOT resolve into a material. A file named &lt;element&gt;__&lt;material&gt;__&lt;group&gt; puts its material at Layer 3 in its own right; where there is no such file the element's material is unknown, and the placeholder is where it sits. An export with none of them gives one placeholder per group holding the whole of it, which is what every case read before 2026-08-31. See CASES.md, `child_layer`. SAFE TO CHANGE: yes -- it is a label.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>data.group_marker</t>
+          <t>data.material_suffix</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>__domain__</t>
+          <t>_mixed</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>groups</t>
+          <t>group_marker</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BY CASE (`groups` in source.csv, semicolon-separated). WHICH GROUPS TO IMPORT.  Empty means all of them.  Narrowing this is the honest way to start: every domain kept is a set of element yields somebody has to supply, and a study of wiring and motors that is properly sourced is worth more than one covering everything on guesses.  The shares are recomputed over whatever is kept, so a restricted run is a self-contained study of those domains rather than a full one with holes in it. What it is NOT is a recovery rate for vehicle electronics as a whole -- the domains left out are simply not in the answer. SAFE TO CHANGE: yes. Names must match upstream: Wiring, Motors, PCB, Sensors.</t>
+          <t>BY CASE (`group_marker` in source.csv). HOW THE UPSTREAM FILES NAME A GROUP'S OWN MASS. Files are `&lt;child&gt;__&lt;parent&gt;.npy`, and the group's own mass is written as `&lt;group_marker&gt;__&lt;group&gt;.npy`. Only change it if the upstream export changes its naming. SAFE TO CHANGE: yes, together with the upstream export.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>data.groups</t>
+          <t>data.group_marker</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>["Wiring", "Motors"]</t>
+          <t>__domain__</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>enabled</t>
+          <t>groups</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RUN THE MONTE CARLO AT ALL. On, because both cases carry value_min and value_max and the spread is the point of running them. A case whose TC table has neither column has nothing to sample -- every draw would return the same number -- and stage 03 says so plainly rather than producing a flat histogram, so leaving this on costs nothing even then.  (This comment used to read "off by default" while the value was True. Found by the documentation sweep on 2026-08-26.) SAFE TO CHANGE: yes.</t>
+          <t>BY CASE (`groups` in source.csv, semicolon-separated). WHICH GROUPS TO IMPORT.  Empty means all of them.  Narrowing this is the honest way to start: every domain kept is a set of element yields somebody has to supply, and a study of wiring and motors that is properly sourced is worth more than one covering everything on guesses.  The shares are recomputed over whatever is kept, so a restricted run is a self-contained study of those domains rather than a full one with holes in it. What it is NOT is a recovery rate for vehicle electronics as a whole -- the domains left out are simply not in the answer. SAFE TO CHANGE: yes. Names must match upstream: Wiring, Motors, PCB, Sensors.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>monte_carlo.enabled</t>
-        </is>
-      </c>
-      <c r="D17" t="b">
-        <v>1</v>
+          <t>data.groups</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>["Wiring", "Motors"]</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>enabled</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>THE SEED.  Shifts every coefficient's stream together. Draw i of a given coefficient is fixed by its identity and this seed, not by a running generator, so it is the same number however the run is chunked and whatever order the table is in. That is what lets two scenarios be compared: the same draw index means the same underlying randomness in both, so the difference between them is the scenario rather than noise. Change it only for a genuinely independent repeat. SAFE TO CHANGE: yes, but a different seed means results that cannot be compared draw by draw with earlier ones.</t>
+          <t>RUN THE MONTE CARLO AT ALL. On, because both cases carry value_min and value_max and the spread is the point of running them. A case whose TC table has neither column has nothing to sample -- every draw would return the same number -- and stage 03 says so plainly rather than producing a flat histogram, so leaving this on costs nothing even then.  (This comment used to read "off by default" while the value was True. Found by the documentation sweep on 2026-08-26.) SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>monte_carlo.seed</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
+          <t>monte_carlo.enabled</t>
+        </is>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>chunk</t>
+          <t>seed</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HOW MANY DRAWS TO HOLD IN MEMORY AT ONCE. The whole result is rows x draws x 8 bytes; at full width that is larger than any machine here has. Draws are therefore processed in blocks and reduced as they go. Lower this if a run runs out of memory; raise it for a little more speed on a small case. SAFE TO CHANGE: yes. It changes nothing about the answer -- a chunked run reproduces an unchunked one exactly, which test_monte_carlo.py checks.</t>
+          <t>THE SEED.  Shifts every coefficient's stream together. Draw i of a given coefficient is fixed by its identity and this seed, not by a running generator, so it is the same number however the run is chunked and whatever order the table is in. That is what lets two scenarios be compared: the same draw index means the same underlying randomness in both, so the difference between them is the scenario rather than noise. Change it only for a genuinely independent repeat. SAFE TO CHANGE: yes, but a different seed means results that cannot be compared draw by draw with earlier ones.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>monte_carlo.chunk</t>
+          <t>monte_carlo.seed</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -829,99 +831,99 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>memory_budget_gb</t>
+          <t>chunk</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HOW MUCH MEMORY THE RUN MAY USE, in gigabytes.  The result is rows x draws x 8 bytes and cannot be avoided if exact percentiles are wanted, so this is what decides whether a run is possible at all. Everything else -- the sampled coefficients, the working values, the sorting scratch -- is transient and is bounded by the chunk, which is sized from this budget rather than guessed.  A run whose result alone exceeds the budget stops BEFORE allocating anything, and says which lever to pull: fewer draws, fewer years, fewer domains. That is the point -- the alternative is the machine swapping for ten minutes and then the process being killed with no explanation.  Raise it if the machine has the memory. 4 GB suits a 16 GB laptop with something else open; 8 suits the 32 GB machine this is developed on, and is what the boards case needs -- 1,661 rows x 200,000 draws is 2.7 GB of result and about 4.5 GB in all, which 4 refused. SAFE TO CHANGE: yes. A number above zero.</t>
+          <t>HOW MANY DRAWS TO HOLD IN MEMORY AT ONCE. The whole result is rows x draws x 8 bytes; at full width that is larger than any machine here has. Draws are therefore processed in blocks and reduced as they go. Lower this if a run runs out of memory; raise it for a little more speed on a small case. SAFE TO CHANGE: yes. It changes nothing about the answer -- a chunked run reproduces an unchunked one exactly, which test_monte_carlo.py checks.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>monte_carlo.memory_budget_gb</t>
+          <t>monte_carlo.chunk</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>sum_to_one</t>
+          <t>memory_budget_gb</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HOW A GROUP WITH NO `is_residual` ROW IS MADE TO SUM TO 1.  'normalise'   divide the group by its own sum. Always works, needs nothing added to the table, and shifts every marginal off the triangular it was drawn from. 'condition'   keep every row's own measurement: draw them all, take the widest as determined by the rest, weight each draw by that row's own density at the value it was forced to, and resample. This is what "sum to 1" means probabilistically -- the product of the measured densities, restricted to the draws that do sum to 1.  Use 'condition' when every row carries a measured range and you want all of them used. It also makes a contradiction visible: ranges that cannot all be true collapse the effective sample size, which stage 03 reports, instead of being silently absorbed.  Groups that DO name a residual row are unaffected. That row has no measurement of its own -- its bounds must be blank -- so there is nothing to condition on, and for a two-row group the residual rule is exact.  SAFE TO CHANGE: yes, but it changes the numbers for any group where every row has a range. It is not a tuning knob; it is a modelling choice.  'normalise' is kept for two reasons and no others: reproducing a result computed before conditioning existed, and getting a number out of a group whose ranges contradict each other, which conditioning refuses. Note what the second one means -- normalising a contradictory group does not resolve the contradiction, it hides it.</t>
+          <t>HOW MUCH MEMORY THE RUN MAY USE, in gigabytes.  The result is rows x draws x 8 bytes and cannot be avoided if exact percentiles are wanted, so this is what decides whether a run is possible at all. Everything else -- the sampled coefficients, the working values, the sorting scratch -- is transient and is bounded by the chunk, which is sized from this budget rather than guessed.  A run whose result alone exceeds the budget stops BEFORE allocating anything, and says which lever to pull: fewer draws, fewer years, fewer domains. That is the point -- the alternative is the machine swapping for ten minutes and then the process being killed with no explanation.  Raise it if the machine has the memory. 4 GB suits a 16 GB laptop with something else open; 8 suits the 32 GB machine this is developed on, and is what the boards case needs -- 1,661 rows x 200,000 draws is 2.7 GB of result and about 4.5 GB in all, which 4 refused. SAFE TO CHANGE: yes. A number above zero.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>monte_carlo.sum_to_one</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>condition</t>
-        </is>
+          <t>monte_carlo.memory_budget_gb</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>png</t>
+          <t>sum_to_one</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WRITE PNG FILES.  On. The picture format -- use it for slides, email, and anything that will not accept a vector file. SAFE TO CHANGE: yes.</t>
+          <t>HOW A GROUP WITH NO `is_residual` ROW IS MADE TO SUM TO 1.  'normalise'   divide the group by its own sum. Always works, needs nothing added to the table, and shifts every marginal off the triangular it was drawn from. 'condition'   keep every row's own measurement: draw them all, take the widest as determined by the rest, weight each draw by that row's own density at the value it was forced to, and resample. This is what "sum to 1" means probabilistically -- the product of the measured densities, restricted to the draws that do sum to 1.  Use 'condition' when every row carries a measured range and you want all of them used. It also makes a contradiction visible: ranges that cannot all be true collapse the effective sample size, which stage 03 reports, instead of being silently absorbed.  Groups that DO name a residual row are unaffected. That row has no measurement of its own -- its bounds must be blank -- so there is nothing to condition on, and for a two-row group the residual rule is exact.  SAFE TO CHANGE: yes, but it changes the numbers for any group where every row has a range. It is not a tuning knob; it is a modelling choice.  'normalise' is kept for two reasons and no others: reproducing a result computed before conditioning existed, and getting a number out of a group whose ranges contradict each other, which conditioning refuses. Note what the second one means -- normalising a contradictory group does not resolve the contradiction, it hides it.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>figures.png</t>
-        </is>
-      </c>
-      <c r="D22" t="b">
-        <v>1</v>
+          <t>monte_carlo.sum_to_one</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>svg</t>
+          <t>png</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WRITE SVG FILES.  Off -- set to True to also get them. A vector format: it stays sharp at any size, and can be opened and edited afterwards in Illustrator or Inkscape. Also the format for web pages. SAFE TO CHANGE: yes.</t>
+          <t>WRITE PNG FILES.  On. The picture format -- use it for slides, email, and anything that will not accept a vector file. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>figures.svg</t>
+          <t>figures.png</t>
         </is>
       </c>
       <c r="D23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>svg</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WRITE PDF FILES.  Off -- set to True to also get them. A vector format with the text kept as real, searchable text. This is the one for reports, papers and printing. SAFE TO CHANGE: yes.</t>
+          <t>WRITE SVG FILES.  Off -- set to True to also get them. A vector format: it stays sharp at any size, and can be opened and edited afterwards in Illustrator or Inkscape. Also the format for web pages. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>figures.pdf</t>
+          <t>figures.svg</t>
         </is>
       </c>
       <c r="D24" t="b">
@@ -931,192 +933,212 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>out_dir</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WHERE THE FIGURES ARE WRITTEN, as a folder name from the project root. The folder is created if it does not exist. SAFE TO CHANGE: yes.</t>
+          <t>WRITE PDF FILES.  Off -- set to True to also get them. A vector format with the text kept as real, searchable text. This is the one for reports, papers and printing. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>figures.out_dir</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>figures</t>
-        </is>
+          <t>figures.pdf</t>
+        </is>
+      </c>
+      <c r="D25" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dpi</t>
+          <t>out_dir</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RESOLUTION OF THE PNG FILES, in dots per inch. Ignored by SVG and PDF, which are vector formats and have no resolution. 200 is roughly print quality at the figure's natural size; 96 gives a smaller file for screen use; 300 is heavier than most documents need. SAFE TO CHANGE: yes. Must be a whole number above zero.</t>
+          <t>WHERE THE FIGURES ARE WRITTEN, as a folder name from the project root. The folder is created if it does not exist. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>figures.dpi</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>200</v>
+          <t>figures.out_dir</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>figures</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>theme</t>
+          <t>dpi</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>COLOUR SCHEME: 'light' or 'dark'. The figures used to follow the reader's system setting automatically. A PNG or PDF cannot do that, so the choice is made when they are drawn. SAFE TO CHANGE: yes.</t>
+          <t>RESOLUTION OF THE PNG FILES, in dots per inch. Ignored by SVG and PDF, which are vector formats and have no resolution. 200 is roughly print quality at the figure's natural size; 96 gives a smaller file for screen use; 300 is heavier than most documents need. SAFE TO CHANGE: yes. Must be a whole number above zero.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>figures.theme</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>light</t>
-        </is>
+          <t>figures.dpi</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>element_figures</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DRAW ONE SANKEY PER ELEMENT, in addition to the total. SAFE TO CHANGE: yes. With many elements this is one file per element per format, which multiplies quickly -- set to False for the total only.</t>
+          <t>COLOUR SCHEME: 'light' or 'dark'. The figures used to follow the reader's system setting automatically. A PNG or PDF cannot do that, so the choice is made when they are drawn. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>figures.element_figures</t>
-        </is>
-      </c>
-      <c r="D28" t="b">
-        <v>1</v>
+          <t>figures.theme</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>resources</t>
+          <t>element_figures</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WHICH RESOURCES THE FIGURES COVER.  Empty means every one the case resolves. Name a few to focus: ('copper',) draws only copper on fate.png, account_&lt;r&gt;.png, fleet_&lt;r&gt;.png and the per-resource densities.  It narrows what is DRAWN and never what is solved. Every resource stays in recovery_results.xlsx and monte_carlo_summary.csv whatever this says, so nothing is lost by focusing -- which is the point: the boards case resolves twenty-odd elements and a reader usually wants two. SAFE TO CHANGE: yes. A name that no case has is ignored rather than silently producing an empty figure.  2026-09-17: nickel, cobalt and lithium joined copper when the battery case arrived. Both spellings of copper are listed because the cases do not agree on it -- wiring resolves MATERIALS and calls it `copper`, boards and the battery resolve ELEMENTS and call it `Cu`. The other three are elements everywhere, so one spelling each.  2026-09-25: the rare earths and the other motor materials joined it. Until the mixed-depth fix this list matched nothing in the traction motor case -- it resolves copper at the MATERIAL layer and the figures only looked at the element layer -- so `chosen` fell back to "everything it can see", which was the four rare earths and nothing else. With the fix 'copper' matches, and a list of five would have narrowed the figures to copper alone and dropped the rare earths. Both belong in this study, so both are named.</t>
+          <t>DRAW ONE SANKEY PER ELEMENT, in addition to the total. SAFE TO CHANGE: yes. With many elements this is one file per element per format, which multiplies quickly -- set to False for the total only.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>figures.resources</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>["copper", "Cu", "Ni", "Co", "Li", "Nd", "Pr", "Dy", "Tb", "aluminium", "steel", "lamination"]</t>
-        </is>
+          <t>figures.element_figures</t>
+        </is>
+      </c>
+      <c r="D29" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cases</t>
+          <t>resources</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WHICH CASES ARE ADDED. Any number; battery packs and drivetrains join by being listed here once they have a case folder of their own. SAFE TO CHANGE: yes. A folder that does not exist is named and refused.</t>
+          <t>WHICH RESOURCES THE FIGURES COVER.  Empty means every one the case resolves. Name a few to focus: ('copper',) draws only copper on fate.png, account_&lt;r&gt;.png, fleet_&lt;r&gt;.png and the per-resource densities.  It narrows what is DRAWN and never what is solved. Every resource stays in recovery_results.xlsx and monte_carlo_summary.csv whatever this says, so nothing is lost by focusing -- which is the point: the boards case resolves twenty-odd elements and a reader usually wants two. SAFE TO CHANGE: yes. A name that no case has is ignored rather than silently producing an empty figure.  2026-09-17: nickel, cobalt and lithium joined copper when the battery case arrived. Both spellings of copper are listed because the cases do not agree on it -- wiring resolves MATERIALS and calls it `copper`, boards and the battery resolve ELEMENTS and call it `Cu`. The other three are elements everywhere, so one spelling each.  2026-09-25: the rare earths and the other motor materials joined it. Until the mixed-depth fix this list matched nothing in the traction motor case -- it resolves copper at the MATERIAL layer and the figures only looked at the element layer -- so `chosen` fell back to "everything it can see", which was the four rare earths and nothing else. With the fix 'copper' matches, and a list of five would have narrowed the figures to copper alone and dropped the rare earths. Both belong in this study, so both are named.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>combine.cases</t>
+          <t>figures.resources</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>["data/bev_electronics_wiring", "data/bev_electronics_boards", "data/battery", "data/tractionmotor"]</t>
+          <t>["copper", "Cu", "Ni", "Co", "Li", "Nd", "Pr", "Dy", "Tb", "aluminium", "steel", "lamination"]</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>resources</t>
+          <t>cases</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>****************************************************************** WHICH METALS ARE DRAWN.  Every one of them, every time 04 is run: four metals x three scenarios is twelve sets of figures from one press of Run. Add a metal by adding a line.  'how a reader says it': ('every spelling the data uses',)  THE SPELLINGS ARE A LIST BECAUSE THE CASES DISAGREE. Wiring resolves MATERIALS and calls it `copper`; boards and the battery resolve ELEMENTS and call it `Cu`. They are the same metal and this is the only place that says so -- every spelling is looked for in every case, and whichever one that case has is the one used. Nickel, cobalt and lithium are elements everywhere, so one spelling each.  The label is what the figures are titled and named with, so `nickel` gives nickel_combined.png and the rest of its set.  SAFE TO CHANGE: yes. A case with none of a metal's spellings is reported as contributing nothing rather than silently counting zero. ******************************************************************  THE RARE EARTHS JOINED ON 2026-09-29, when the traction motor case did. They were left out while there were FOUR traction cases, because those were competing routes for the same motors and adding them would have counted one fleet four times. There is one traction case now -- both roads inside it, split at the review's step 2 -- so it adds like any other part of the car.  Nd and Dy are in the BOARDS case too, as sensor and actuator magnets. That is not a double count: a sensor magnet and a traction magnet are different components of the same vehicle, which is the same reason wiring copper and board copper are added.</t>
+          <t>WHICH CASES ARE ADDED. Any number; battery packs and drivetrains join by being listed here once they have a case folder of their own. SAFE TO CHANGE: yes. A folder that does not exist is named and refused.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>combine.resources</t>
+          <t>combine.cases</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>{'copper': ('copper', 'Cu'), 'nickel': ('Ni',), 'cobalt': ('Co',), 'lithium': ('Li',), 'neodymium': ('Nd',), 'praseodymium': ('Pr',), 'dysprosium': ('Dy',), 'terbium': ('Tb',)}</t>
+          <t>["data/bev_electronics_wiring", "data/bev_electronics_boards", "data/battery", "data/tractionmotor"]</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>whole</t>
+          <t>resources</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>What the combined streams are called together, for the title. Updated 2026-09-17 when the battery joined `cases`: the figures were still titled 'BEV electronics' while drawing the battery's components alongside them. SAFE TO CHANGE: yes.</t>
+          <t>****************************************************************** WHICH METALS ARE DRAWN.  Every one of them, every time 04 is run: four metals x three scenarios is twelve sets of figures from one press of Run. Add a metal by adding a line.  'how a reader says it': ('every spelling the data uses',)  THE SPELLINGS ARE A LIST BECAUSE THE CASES DISAGREE. Wiring resolves MATERIALS and calls it `copper`; boards and the battery resolve ELEMENTS and call it `Cu`. They are the same metal and this is the only place that says so -- every spelling is looked for in every case, and whichever one that case has is the one used. Nickel, cobalt and lithium are elements everywhere, so one spelling each.  The label is what the figures are titled and named with, so `nickel` gives nickel_combined.png and the rest of its set.  SAFE TO CHANGE: yes. A case with none of a metal's spellings is reported as contributing nothing rather than silently counting zero. ******************************************************************  THE RARE EARTHS JOINED ON 2026-09-29, when the traction motor case did. They were left out while there were FOUR traction cases, because those were competing routes for the same motors and adding them would have counted one fleet four times. There is one traction case now -- both roads inside it, split at the review's step 2 -- so it adds like any other part of the car.  Nd and Dy are in the BOARDS case too, as sensor and actuator magnets. That is not a double count: a sensor magnet and a traction magnet are different components of the same vehicle, which is the same reason wiring copper and board copper are added.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>combine.whole</t>
+          <t>combine.resources</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>BEV electronics, battery and traction motor</t>
+          <t>{'copper': ('copper', 'Cu'), 'nickel': ('Ni',), 'cobalt': ('Co',), 'lithium': ('Li',), 'neodymium': ('Nd',), 'praseodymium': ('Pr',), 'dysprosium': ('Dy',), 'terbium': ('Tb',)}</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>whole</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>What the combined streams are called together, for the title. Updated 2026-09-17 when the battery joined `cases`: the figures were still titled 'BEV electronics' while drawing the battery's components alongside them. SAFE TO CHANGE: yes.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>combine.whole</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>BEV electronics, battery and traction motor</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>out_dir</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>WHERE THE COMBINED FIGURE GOES. Not any one case's folder: it belongs to none of them. SAFE TO CHANGE: yes.</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>combine.out_dir</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>figures/combined</t>
         </is>

--- a/params.xlsx
+++ b/params.xlsx
@@ -1064,7 +1064,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>WHICH CASES ARE ADDED. Any number; battery packs and drivetrains join by being listed here once they have a case folder of their own. SAFE TO CHANGE: yes. A folder that does not exist is named and refused.</t>
+          <t>WHICH CASES ARE ADDED. Any number; battery packs and drivetrains join by being listed here once they have a case folder of their own. SAFE TO CHANGE: yes. A folder that does not exist is named and refused.  THE BATTERY IS FIVE CASES, one per chemistry (2026-10-09; `data/battery`, the one blended case, is no longer here: its input check refuses S2 and S3, which carry the sodium cells). A case that does not have the scenario of a pass -- sodium has no S1, solid-state has neither S1 nor S2 -- is left out of that pass with a line saying so, so the three scenarios add three, four and five battery cases in turn. THE FIRST CASE LISTED THAT HAS SCENARIOS DECIDES WHICH PASSES ARE MADE, so the one that has all of them (LFP) comes first of the battery cases. Put sodium first and S1 is not run.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>["data/bev_electronics_wiring", "data/bev_electronics_boards", "data/battery", "data/tractionmotor"]</t>
+          <t>["data/bev_electronics_wiring", "data/bev_electronics_boards", "data/battery_lfp", "data/battery_lmfp", "data/battery_nmc_high", "data/battery_sodium", "data/battery_solid_state", "data/tractionmotor"]</t>
         </is>
       </c>
     </row>
